--- a/markdown_generator/pubs.xlsx
+++ b/markdown_generator/pubs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github Projects/wonchan-choi.github.io/markdown_generator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wchoi/Github-Repositories/wonchan-choi.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C986CD4-81DF-BD48-9E1A-26109C129277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5718BCF8-E0E0-784C-9A16-BC97E007D10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="500" windowWidth="34400" windowHeight="19420" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
+    <workbookView xWindow="1360" yWindow="500" windowWidth="42600" windowHeight="24200" xr2:uid="{C1244F33-F08D-274A-A656-7DB80AA6BA4E}"/>
   </bookViews>
   <sheets>
     <sheet name="publications" sheetId="1" r:id="rId1"/>
@@ -1377,15 +1377,12 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1777,290 +1774,290 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="74.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.5" style="2"/>
-    <col min="3" max="3" width="21.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="62.5" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="74.5" style="2"/>
+    <col min="2" max="2" width="74.5" style="1"/>
+    <col min="3" max="3" width="21.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="62.5" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="74.5" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="323" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>2023</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2003</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>2022</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>2022</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>2022</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>2022</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>2021</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>2020</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>2020</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>2019</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>2019</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>2017</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>2016</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>2015</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="51" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>2015</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="68" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>2015</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="68" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>2008</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="51" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>2008</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>19</v>
       </c>
     </row>
